--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka, Stefan Andersson</t>
+          <t>Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124773355</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1083 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125738062</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79046</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>864</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Buolžavárri, Buolžavárri, T lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>703014</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7529224</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka, Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125735743</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91627</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Buolžavárri, Buolžavárri, T lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703036</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7529196</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka, Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125742767</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79046</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>864</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Puoltsavaara, Puoltsavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>703191</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7529445</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka, Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125735087</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Buolžavárri, Buolžavárri, T lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>703061</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7529206</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka, Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125886402</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>702972</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7529510</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125886462</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703239</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7529510</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125886625</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57807</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>702968</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7529363</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125886448</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703118</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7529601</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125886390</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702960</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7529290</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125886383</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Puoltsa, T lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702968</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7529363</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka, Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka, Christina Boyd, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91627</v>
+        <v>91634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125738062</v>
       </c>
       <c r="B3" t="n">
-        <v>79046</v>
+        <v>79047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka, Christina Boyd, Anna Öhlund, Stefan Andersson</t>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91634</v>
+        <v>91638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125742767</v>
       </c>
       <c r="B5" t="n">
-        <v>79046</v>
+        <v>79047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125886448</v>
+        <v>125886390</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703118</v>
+        <v>702960</v>
       </c>
       <c r="R10" t="n">
-        <v>7529601</v>
+        <v>7529290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125886390</v>
+        <v>125886448</v>
       </c>
       <c r="B11" t="n">
         <v>57651</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702960</v>
+        <v>703118</v>
       </c>
       <c r="R11" t="n">
-        <v>7529290</v>
+        <v>7529601</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125738062</v>
       </c>
       <c r="B3" t="n">
-        <v>79047</v>
+        <v>79051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91638</v>
+        <v>91642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125742767</v>
       </c>
       <c r="B5" t="n">
-        <v>79047</v>
+        <v>79051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, per-erik mukka, Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125886462</v>
+        <v>125886625</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57807</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,29 +1341,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703239</v>
+        <v>702968</v>
       </c>
       <c r="R8" t="n">
-        <v>7529510</v>
+        <v>7529363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,17 +1432,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125886625</v>
+        <v>125886462</v>
       </c>
       <c r="B9" t="n">
-        <v>57807</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,33 +1450,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702968</v>
+        <v>703239</v>
       </c>
       <c r="R9" t="n">
-        <v>7529363</v>
+        <v>7529510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125886390</v>
+        <v>125886448</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702960</v>
+        <v>703118</v>
       </c>
       <c r="R10" t="n">
-        <v>7529290</v>
+        <v>7529601</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125886448</v>
+        <v>125886390</v>
       </c>
       <c r="B11" t="n">
         <v>57651</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703118</v>
+        <v>702960</v>
       </c>
       <c r="R11" t="n">
-        <v>7529601</v>
+        <v>7529290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125886625</v>
+        <v>125886462</v>
       </c>
       <c r="B8" t="n">
-        <v>57807</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,33 +1341,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1377,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702968</v>
+        <v>703239</v>
       </c>
       <c r="R8" t="n">
-        <v>7529363</v>
+        <v>7529510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,17 +1428,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125886462</v>
+        <v>125886625</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,29 +1446,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703239</v>
+        <v>702968</v>
       </c>
       <c r="R9" t="n">
-        <v>7529510</v>
+        <v>7529363</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125738062</v>
       </c>
       <c r="B3" t="n">
-        <v>79051</v>
+        <v>79052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91642</v>
+        <v>91644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125742767</v>
       </c>
       <c r="B5" t="n">
-        <v>79051</v>
+        <v>79052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125886402</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>125886462</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>125886625</v>
       </c>
       <c r="B9" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125886448</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>125886390</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>125886383</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91646</v>
+        <v>91648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare, Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125738062</v>
       </c>
       <c r="B3" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125735743</v>
       </c>
       <c r="B4" t="n">
-        <v>91648</v>
+        <v>91652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125742767</v>
       </c>
       <c r="B5" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125735087</v>
       </c>
       <c r="B6" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125886402</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>125886462</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
         <v>125886625</v>
       </c>
       <c r="B9" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125886448</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
         <v>125886390</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Flygare, Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
         <v>125886383</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare, Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125886462</v>
+        <v>125886625</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,29 +1341,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703239</v>
+        <v>702968</v>
       </c>
       <c r="R8" t="n">
-        <v>7529510</v>
+        <v>7529363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,17 +1432,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125886625</v>
+        <v>125886462</v>
       </c>
       <c r="B9" t="n">
-        <v>57812</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,33 +1450,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702968</v>
+        <v>703239</v>
       </c>
       <c r="R9" t="n">
-        <v>7529363</v>
+        <v>7529510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1323,17 +1323,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125886625</v>
+        <v>125886462</v>
       </c>
       <c r="B8" t="n">
-        <v>57812</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,33 +1341,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1377,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702968</v>
+        <v>703239</v>
       </c>
       <c r="R8" t="n">
-        <v>7529363</v>
+        <v>7529510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,17 +1428,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125886462</v>
+        <v>125886625</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,29 +1446,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703239</v>
+        <v>702968</v>
       </c>
       <c r="R9" t="n">
-        <v>7529510</v>
+        <v>7529363</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>125886402</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>125886462</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
         <v>125886625</v>
       </c>
       <c r="B9" t="n">
-        <v>57812</v>
+        <v>57813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125886448</v>
+        <v>125886390</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703118</v>
+        <v>702960</v>
       </c>
       <c r="R10" t="n">
-        <v>7529601</v>
+        <v>7529290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,17 +1642,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson, Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125886390</v>
+        <v>125886448</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702960</v>
+        <v>703118</v>
       </c>
       <c r="R11" t="n">
-        <v>7529290</v>
+        <v>7529601</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robert Flygare, Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
         <v>125886383</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17891-2025 artfynd.xlsx
+++ b/artfynd/A 17891-2025 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125886462</v>
+        <v>125886625</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,29 +1341,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703239</v>
+        <v>702968</v>
       </c>
       <c r="R8" t="n">
-        <v>7529510</v>
+        <v>7529363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,17 +1432,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125886625</v>
+        <v>125886462</v>
       </c>
       <c r="B9" t="n">
-        <v>57813</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,33 +1450,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702968</v>
+        <v>703239</v>
       </c>
       <c r="R9" t="n">
-        <v>7529363</v>
+        <v>7529510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, Stefan Andersson, per-erik mukka, Anna Öhlund, Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125886390</v>
+        <v>125886448</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702960</v>
+        <v>703118</v>
       </c>
       <c r="R10" t="n">
-        <v>7529290</v>
+        <v>7529601</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125886448</v>
+        <v>125886390</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703118</v>
+        <v>702960</v>
       </c>
       <c r="R11" t="n">
-        <v>7529601</v>
+        <v>7529290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
